--- a/winterGame2026/冬制作_2026コスト表.xlsx
+++ b/winterGame2026/冬制作_2026コスト表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawanamihakuto\Desktop\GitHub\2026_winter\winterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011DC99C-CD60-4C8F-9E06-C0F382D03E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E87DF5C-047F-4016-9C73-8797A35D616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3495" yWindow="1035" windowWidth="21600" windowHeight="13350" xr2:uid="{FBF17539-65CE-42B3-B6F8-B994C8DD201F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{FBF17539-65CE-42B3-B6F8-B994C8DD201F}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="218">
   <si>
     <t>担当者</t>
   </si>
@@ -633,6 +633,88 @@
   </si>
   <si>
     <t>要望</t>
+  </si>
+  <si>
+    <t>完了</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>AttackEditorSceneとして実装（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>実装済み（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>PlayerIdleState（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>PlayerWalkState（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>PlayerStepState forward/back（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>PlayerStepState sideIn/sideOut（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>IsOpponentOnRight／ToScreenDirection（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>AttackData.csvの読み込み・保存（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>作業中</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jabとして実装、ヒット時の処理は未接続（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>LungeJabとして実装、ヒット時の処理は未接続（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BattleCollision（押し戻し・ヒット検出）（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Collision::Intersect（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ボーン追従のやられ判定13個（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>HitBoxSet::StartAttack／EndAttack（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BattleCollision::ResolvePush（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>HitBoxSet::Draw（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jab・LungeJabを導入済み（10/28確認）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>攻撃ヒットをバトルに接続（判定→通知→ダメージ・のけぞり）</t>
+  </si>
+  <si>
+    <t>ResolveHitsは攻撃IDの記録のみ（10/28確認）</t>
   </si>
 </sst>
 </file>
@@ -646,7 +728,7 @@
     <numFmt numFmtId="179" formatCode="0.0&quot;時間&quot;"/>
     <numFmt numFmtId="180" formatCode="d"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -778,6 +860,14 @@
       <name val="Meiryo"/>
       <family val="3"/>
       <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="27">
@@ -967,7 +1057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1213,6 +1303,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1566,8 +1668,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC9F270B-EF5F-4AFE-9549-39B2F9CB1AAB}" name="タスク" displayName="タスク" ref="B2:J106" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
-  <autoFilter ref="B2:J106" xr:uid="{BC9F270B-EF5F-4AFE-9549-39B2F9CB1AAB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC9F270B-EF5F-4AFE-9549-39B2F9CB1AAB}" name="タスク" displayName="タスク" ref="B2:J107" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+  <autoFilter ref="B2:J107" xr:uid="{BC9F270B-EF5F-4AFE-9549-39B2F9CB1AAB}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{212961F9-CB6C-4E2C-BEF6-955261EA89AF}" name="担当者" dataDxfId="20"/>
     <tableColumn id="2" xr3:uid="{0750B9F1-340F-404B-90DA-B54B51CB66F8}" name="概要" dataDxfId="19"/>
@@ -1900,7 +2002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A017276B-2E2B-466F-8FAA-AAD22BE14252}">
-  <dimension ref="B2:P106"/>
+  <dimension ref="B2:P107"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="2.625" customWidth="1"/>
@@ -2081,19 +2183,19 @@
       </c>
       <c r="M6" s="45">
         <f>SUM(タスク[作業工数])</f>
-        <v>152.9</v>
+        <v>153.9</v>
       </c>
       <c r="N6" s="45">
         <f>SUMIF(タスク[ステータス],"完了",タスク[作業工数])</f>
-        <v>19.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="O6" s="45">
         <f>M6-N6</f>
-        <v>133.4</v>
+        <v>115.7</v>
       </c>
       <c r="P6" s="47">
         <f>IF(M6=0,0,N6/M6)</f>
-        <v>0.12753433616742968</v>
+        <v>0.24821312540610788</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2127,19 +2229,19 @@
       </c>
       <c r="M7" s="45">
         <f>SUMIF(タスク[バージョン],L7,タスク[作業工数])</f>
-        <v>82.4</v>
+        <v>83.4</v>
       </c>
       <c r="N7" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[バージョン],L7,タスク[ステータス],"完了")</f>
-        <v>19.5</v>
+        <v>38.200000000000003</v>
       </c>
       <c r="O7" s="45">
         <f>M7-N7</f>
-        <v>62.900000000000006</v>
+        <v>45.2</v>
       </c>
       <c r="P7" s="47">
         <f>IF(M7=0,0,N7/M7)</f>
-        <v>0.23665048543689318</v>
+        <v>0.45803357314148679</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2255,10 +2357,10 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J10" t="s">
-        <v>27</v>
+        <v>198</v>
       </c>
       <c r="L10" s="29" t="s">
         <v>142</v>
@@ -2388,15 +2490,15 @@
       </c>
       <c r="N13" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L13,タスク[ステータス],"完了")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O13" s="45">
         <f t="shared" ref="O13:O27" si="0">M13-N13</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P13" s="47">
         <f t="shared" ref="P13:P27" si="1">IF(M13=0,0,N13/M13)</f>
-        <v>0.76923076923076927</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:16">
@@ -2480,15 +2582,15 @@
       </c>
       <c r="N15" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L15,タスク[ステータス],"完了")</f>
-        <v>1</v>
+        <v>6.7</v>
       </c>
       <c r="O15" s="45">
         <f t="shared" si="0"/>
-        <v>6.9</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="P15" s="47">
         <f t="shared" si="1"/>
-        <v>0.12658227848101264</v>
+        <v>0.84810126582278478</v>
       </c>
     </row>
     <row r="16" spans="2:16">
@@ -2526,15 +2628,15 @@
       </c>
       <c r="N16" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L16,タスク[ステータス],"完了")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" s="45">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P16" s="47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
     <row r="17" spans="2:16">
@@ -2618,15 +2720,15 @@
       </c>
       <c r="N18" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L18,タスク[ステータス],"完了")</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O18" s="45">
         <f t="shared" si="0"/>
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="P18" s="47">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.84210526315789469</v>
       </c>
     </row>
     <row r="19" spans="2:16">
@@ -2650,17 +2752,17 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="J19" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
       <c r="L19" s="36" t="s">
         <v>86</v>
       </c>
       <c r="M19" s="45">
         <f>SUMIF(タスク[概要],L19,タスク[作業工数])</f>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="N19" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L19,タスク[ステータス],"完了")</f>
@@ -2668,7 +2770,7 @@
       </c>
       <c r="O19" s="45">
         <f t="shared" si="0"/>
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="P19" s="47">
         <f t="shared" si="1"/>
@@ -2696,10 +2798,10 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="J20" t="s">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="L20" s="37" t="s">
         <v>92</v>
@@ -2788,10 +2890,10 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J22" t="s">
-        <v>27</v>
+        <v>201</v>
       </c>
       <c r="L22" s="39" t="s">
         <v>108</v>
@@ -2834,10 +2936,10 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J23" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
       <c r="L23" s="40" t="s">
         <v>115</v>
@@ -2880,10 +2982,10 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J24" t="s">
-        <v>27</v>
+        <v>203</v>
       </c>
       <c r="L24" s="41" t="s">
         <v>119</v>
@@ -2972,10 +3074,10 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J26" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="L26" s="43" t="s">
         <v>133</v>
@@ -3064,10 +3166,10 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J28" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="2:16">
@@ -3091,10 +3193,10 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="J29" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
       <c r="L29" s="23" t="s">
         <v>7</v>
@@ -3137,11 +3239,11 @@
       </c>
       <c r="M30" s="25">
         <f>COUNTIF(タスク[ステータス],L30)</f>
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="N30" s="45">
         <f>SUMIF(タスク[ステータス],L30,タスク[作業工数])</f>
-        <v>128.19999999999999</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -3165,21 +3267,21 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="J31" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="L31" s="25" t="s">
         <v>34</v>
       </c>
       <c r="M31" s="25">
         <f>COUNTIF(タスク[ステータス],L31)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N31" s="45">
         <f>SUMIF(タスク[ステータス],L31,タスク[作業工数])</f>
-        <v>5.2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="32" spans="2:16">
@@ -3213,11 +3315,11 @@
       </c>
       <c r="M32" s="25">
         <f>COUNTIF(タスク[ステータス],L32)</f>
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="N32" s="45">
         <f>SUMIF(タスク[ステータス],L32,タスク[作業工数])</f>
-        <v>19.5</v>
+        <v>38.200000000000003</v>
       </c>
     </row>
     <row r="33" spans="2:14">
@@ -3786,10 +3888,10 @@
       </c>
       <c r="H52" s="3"/>
       <c r="I52" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J52" t="s">
-        <v>27</v>
+        <v>209</v>
       </c>
     </row>
     <row r="53" spans="2:10">
@@ -3813,10 +3915,10 @@
       </c>
       <c r="H53" s="3"/>
       <c r="I53" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J53" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="2:10">
@@ -3840,10 +3942,10 @@
       </c>
       <c r="H54" s="3"/>
       <c r="I54" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J54" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
     </row>
     <row r="55" spans="2:10">
@@ -3867,10 +3969,10 @@
       </c>
       <c r="H55" s="3"/>
       <c r="I55" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J55" t="s">
-        <v>27</v>
+        <v>210</v>
       </c>
     </row>
     <row r="56" spans="2:10">
@@ -3894,10 +3996,10 @@
       </c>
       <c r="H56" s="3"/>
       <c r="I56" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J56" t="s">
-        <v>27</v>
+        <v>211</v>
       </c>
     </row>
     <row r="57" spans="2:10">
@@ -3921,10 +4023,10 @@
       </c>
       <c r="H57" s="3"/>
       <c r="I57" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J57" t="s">
-        <v>27</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" spans="2:10">
@@ -3948,10 +4050,10 @@
       </c>
       <c r="H58" s="3"/>
       <c r="I58" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J58" t="s">
-        <v>27</v>
+        <v>213</v>
       </c>
     </row>
     <row r="59" spans="2:10">
@@ -4002,37 +4104,37 @@
       </c>
       <c r="H60" s="3"/>
       <c r="I60" t="s">
-        <v>26</v>
+        <v>197</v>
       </c>
       <c r="J60" t="s">
-        <v>39</v>
+        <v>214</v>
       </c>
     </row>
     <row r="61" spans="2:10">
-      <c r="B61" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="11" t="s">
+      <c r="B61" s="82" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="85" t="s">
         <v>86</v>
       </c>
-      <c r="D61" t="s">
-        <v>87</v>
-      </c>
-      <c r="E61" t="s">
+      <c r="D61" s="83" t="s">
+        <v>216</v>
+      </c>
+      <c r="E61" s="83" t="s">
         <v>12</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F61" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="3">
+      <c r="G61" s="84">
         <v>1</v>
       </c>
-      <c r="H61" s="3"/>
-      <c r="I61" t="s">
-        <v>26</v>
-      </c>
-      <c r="J61" t="s">
-        <v>39</v>
+      <c r="H61" s="84"/>
+      <c r="I61" s="83" t="s">
+        <v>34</v>
+      </c>
+      <c r="J61" s="83" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="62" spans="2:10">
@@ -4043,16 +4145,16 @@
         <v>86</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E62" t="s">
         <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G62" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" t="s">
@@ -4070,16 +4172,16 @@
         <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E63" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F63" t="s">
         <v>38</v>
       </c>
       <c r="G63" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" t="s">
@@ -4097,7 +4199,7 @@
         <v>86</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E64" t="s">
         <v>22</v>
@@ -4106,7 +4208,7 @@
         <v>38</v>
       </c>
       <c r="G64" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" t="s">
@@ -4124,7 +4226,7 @@
         <v>86</v>
       </c>
       <c r="D65" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
         <v>22</v>
@@ -4133,7 +4235,7 @@
         <v>38</v>
       </c>
       <c r="G65" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" t="s">
@@ -4147,27 +4249,27 @@
       <c r="B66" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>92</v>
+      <c r="C66" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F66" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G66" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3"/>
       <c r="I66" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J66" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67" spans="2:10">
@@ -4178,7 +4280,7 @@
         <v>92</v>
       </c>
       <c r="D67" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E67" t="s">
         <v>12</v>
@@ -4187,14 +4289,14 @@
         <v>13</v>
       </c>
       <c r="G67" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H67" s="3"/>
       <c r="I67" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J67" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="2:10">
@@ -4205,7 +4307,7 @@
         <v>92</v>
       </c>
       <c r="D68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E68" t="s">
         <v>12</v>
@@ -4232,7 +4334,7 @@
         <v>92</v>
       </c>
       <c r="D69" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E69" t="s">
         <v>12</v>
@@ -4259,7 +4361,7 @@
         <v>92</v>
       </c>
       <c r="D70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E70" t="s">
         <v>12</v>
@@ -4268,7 +4370,7 @@
         <v>13</v>
       </c>
       <c r="G70" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" t="s">
@@ -4286,7 +4388,7 @@
         <v>92</v>
       </c>
       <c r="D71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E71" t="s">
         <v>12</v>
@@ -4313,16 +4415,16 @@
         <v>92</v>
       </c>
       <c r="D72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E72" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G72" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" t="s">
@@ -4340,7 +4442,7 @@
         <v>92</v>
       </c>
       <c r="D73" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E73" t="s">
         <v>22</v>
@@ -4363,27 +4465,27 @@
       <c r="B74" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C74" s="13" t="s">
-        <v>101</v>
+      <c r="C74" s="12" t="s">
+        <v>92</v>
       </c>
       <c r="D74" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E74" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F74" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G74" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J74" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="2:10">
@@ -4394,23 +4496,23 @@
         <v>101</v>
       </c>
       <c r="D75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E75" t="s">
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G75" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" t="s">
         <v>34</v>
       </c>
       <c r="J75" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="2:10">
@@ -4421,7 +4523,7 @@
         <v>101</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E76" t="s">
         <v>12</v>
@@ -4430,11 +4532,11 @@
         <v>38</v>
       </c>
       <c r="G76" s="3">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H76" s="3"/>
       <c r="I76" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J76" t="s">
         <v>27</v>
@@ -4448,23 +4550,23 @@
         <v>101</v>
       </c>
       <c r="D77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E77" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
         <v>38</v>
       </c>
       <c r="G77" s="3">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" t="s">
         <v>26</v>
       </c>
       <c r="J77" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78" spans="2:10">
@@ -4475,16 +4577,16 @@
         <v>101</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E78" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="G78" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" t="s">
@@ -4498,17 +4600,17 @@
       <c r="B79" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C79" s="14" t="s">
-        <v>108</v>
+      <c r="C79" s="13" t="s">
+        <v>101</v>
       </c>
       <c r="D79" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E79" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F79" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="G79" s="3">
         <v>1</v>
@@ -4529,10 +4631,10 @@
         <v>108</v>
       </c>
       <c r="D80" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E80" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F80" t="s">
         <v>38</v>
@@ -4556,7 +4658,7 @@
         <v>108</v>
       </c>
       <c r="D81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E81" t="s">
         <v>22</v>
@@ -4565,7 +4667,7 @@
         <v>38</v>
       </c>
       <c r="G81" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H81" s="3"/>
       <c r="I81" t="s">
@@ -4583,7 +4685,7 @@
         <v>108</v>
       </c>
       <c r="D82" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E82" t="s">
         <v>22</v>
@@ -4592,7 +4694,7 @@
         <v>38</v>
       </c>
       <c r="G82" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H82" s="3"/>
       <c r="I82" t="s">
@@ -4610,16 +4712,16 @@
         <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E83" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F83" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="G83" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H83" s="3"/>
       <c r="I83" t="s">
@@ -4637,7 +4739,7 @@
         <v>108</v>
       </c>
       <c r="D84" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E84" t="s">
         <v>24</v>
@@ -4646,7 +4748,7 @@
         <v>107</v>
       </c>
       <c r="G84" s="3">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H84" s="3"/>
       <c r="I84" t="s">
@@ -4660,27 +4762,27 @@
       <c r="B85" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C85" s="15" t="s">
-        <v>115</v>
+      <c r="C85" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="D85" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E85" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F85" t="s">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="G85" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H85" s="3"/>
       <c r="I85" t="s">
         <v>26</v>
       </c>
       <c r="J85" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" spans="2:10">
@@ -4691,7 +4793,7 @@
         <v>115</v>
       </c>
       <c r="D86" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E86" t="s">
         <v>22</v>
@@ -4714,27 +4816,27 @@
       <c r="B87" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C87" s="16" t="s">
-        <v>119</v>
+      <c r="C87" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="D87" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E87" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F87" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G87" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="J87" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="88" spans="2:10">
@@ -4745,7 +4847,7 @@
         <v>119</v>
       </c>
       <c r="D88" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E88" t="s">
         <v>12</v>
@@ -4754,14 +4856,14 @@
         <v>13</v>
       </c>
       <c r="G88" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H88" s="3"/>
       <c r="I88" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J88" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
     </row>
     <row r="89" spans="2:10">
@@ -4772,7 +4874,7 @@
         <v>119</v>
       </c>
       <c r="D89" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E89" t="s">
         <v>12</v>
@@ -4781,14 +4883,14 @@
         <v>13</v>
       </c>
       <c r="G89" s="3">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="H89" s="3"/>
       <c r="I89" t="s">
-        <v>26</v>
+        <v>206</v>
       </c>
       <c r="J89" t="s">
-        <v>39</v>
+        <v>215</v>
       </c>
     </row>
     <row r="90" spans="2:10">
@@ -4799,16 +4901,16 @@
         <v>119</v>
       </c>
       <c r="D90" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E90" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="G90" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H90" s="3"/>
       <c r="I90" t="s">
@@ -4826,7 +4928,7 @@
         <v>119</v>
       </c>
       <c r="D91" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E91" t="s">
         <v>22</v>
@@ -4853,7 +4955,7 @@
         <v>119</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E92" t="s">
         <v>22</v>
@@ -4880,7 +4982,7 @@
         <v>119</v>
       </c>
       <c r="D93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E93" t="s">
         <v>22</v>
@@ -4889,7 +4991,7 @@
         <v>38</v>
       </c>
       <c r="G93" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H93" s="3"/>
       <c r="I93" t="s">
@@ -4903,11 +5005,11 @@
       <c r="B94" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C94" s="17" t="s">
-        <v>128</v>
+      <c r="C94" s="16" t="s">
+        <v>119</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E94" t="s">
         <v>22</v>
@@ -4916,7 +5018,7 @@
         <v>38</v>
       </c>
       <c r="G94" s="3">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="H94" s="3"/>
       <c r="I94" t="s">
@@ -4934,7 +5036,7 @@
         <v>128</v>
       </c>
       <c r="D95" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E95" t="s">
         <v>22</v>
@@ -4943,7 +5045,7 @@
         <v>38</v>
       </c>
       <c r="G95" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H95" s="3"/>
       <c r="I95" t="s">
@@ -4961,7 +5063,7 @@
         <v>128</v>
       </c>
       <c r="D96" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E96" t="s">
         <v>22</v>
@@ -4970,7 +5072,7 @@
         <v>38</v>
       </c>
       <c r="G96" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" t="s">
@@ -4988,16 +5090,16 @@
         <v>128</v>
       </c>
       <c r="D97" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E97" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
         <v>38</v>
       </c>
       <c r="G97" s="3">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" t="s">
@@ -5011,20 +5113,20 @@
       <c r="B98" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C98" s="18" t="s">
-        <v>133</v>
+      <c r="C98" s="17" t="s">
+        <v>128</v>
       </c>
       <c r="D98" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E98" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F98" t="s">
         <v>38</v>
       </c>
       <c r="G98" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H98" s="3"/>
       <c r="I98" t="s">
@@ -5042,7 +5144,7 @@
         <v>133</v>
       </c>
       <c r="D99" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E99" t="s">
         <v>22</v>
@@ -5051,7 +5153,7 @@
         <v>38</v>
       </c>
       <c r="G99" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H99" s="3"/>
       <c r="I99" t="s">
@@ -5069,16 +5171,16 @@
         <v>133</v>
       </c>
       <c r="D100" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E100" t="s">
         <v>22</v>
       </c>
       <c r="F100" t="s">
-        <v>107</v>
+        <v>38</v>
       </c>
       <c r="G100" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H100" s="3"/>
       <c r="I100" t="s">
@@ -5092,11 +5194,11 @@
       <c r="B101" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C101" s="19" t="s">
-        <v>137</v>
+      <c r="C101" s="18" t="s">
+        <v>133</v>
       </c>
       <c r="D101" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E101" t="s">
         <v>22</v>
@@ -5105,7 +5207,7 @@
         <v>107</v>
       </c>
       <c r="G101" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H101" s="3"/>
       <c r="I101" t="s">
@@ -5123,7 +5225,7 @@
         <v>137</v>
       </c>
       <c r="D102" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E102" t="s">
         <v>22</v>
@@ -5132,7 +5234,7 @@
         <v>107</v>
       </c>
       <c r="G102" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H102" s="3"/>
       <c r="I102" t="s">
@@ -5150,16 +5252,16 @@
         <v>137</v>
       </c>
       <c r="D103" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E103" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F103" t="s">
         <v>107</v>
       </c>
       <c r="G103" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H103" s="3"/>
       <c r="I103" t="s">
@@ -5177,13 +5279,13 @@
         <v>137</v>
       </c>
       <c r="D104" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E104" t="s">
         <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="G104" s="3">
         <v>4</v>
@@ -5204,7 +5306,7 @@
         <v>137</v>
       </c>
       <c r="D105" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E105" t="s">
         <v>12</v>
@@ -5213,7 +5315,7 @@
         <v>142</v>
       </c>
       <c r="G105" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H105" s="3"/>
       <c r="I105" t="s">
@@ -5231,16 +5333,16 @@
         <v>137</v>
       </c>
       <c r="D106" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E106" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F106" t="s">
         <v>142</v>
       </c>
       <c r="G106" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H106" s="3"/>
       <c r="I106" t="s">
@@ -5250,9 +5352,36 @@
         <v>39</v>
       </c>
     </row>
+    <row r="107" spans="2:10">
+      <c r="B107" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D107" t="s">
+        <v>144</v>
+      </c>
+      <c r="E107" t="s">
+        <v>22</v>
+      </c>
+      <c r="F107" t="s">
+        <v>142</v>
+      </c>
+      <c r="G107" s="3">
+        <v>3</v>
+      </c>
+      <c r="H107" s="3"/>
+      <c r="I107" t="s">
+        <v>26</v>
+      </c>
+      <c r="J107" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4"/>
-  <conditionalFormatting sqref="I3:I106">
+  <conditionalFormatting sqref="I3:I107">
     <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
       <formula>$I3="完了"</formula>
     </cfRule>
@@ -5264,13 +5393,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E106" xr:uid="{D9F46512-A4FF-49EA-A99C-53B8AEF55E96}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3:E107" xr:uid="{D9F46512-A4FF-49EA-A99C-53B8AEF55E96}">
       <formula1>"S,A,B,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F106" xr:uid="{30910123-5B1C-4059-ACD0-DD0604EA4B92}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F107" xr:uid="{30910123-5B1C-4059-ACD0-DD0604EA4B92}">
       <formula1>"プロト,アルファ,ベータ,マスター"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I106" xr:uid="{39085DAC-8730-49EC-B3A4-EE7F16B478CE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I107" xr:uid="{39085DAC-8730-49EC-B3A4-EE7F16B478CE}">
       <formula1>"未着手,作業中,完了,保留"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5401,23 +5530,23 @@
       </c>
       <c r="M4" s="56">
         <f ca="1">MAX(0,L4-TODAY()+1)</f>
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="N4" s="57">
         <f>SUMIF(タスク[バージョン],J4,タスク[作業工数])</f>
-        <v>82.4</v>
+        <v>83.4</v>
       </c>
       <c r="O4" s="57">
         <f>N4-SUMIFS(タスク[作業工数],タスク[バージョン],J4,タスク[ステータス],"完了")</f>
-        <v>62.900000000000006</v>
+        <v>45.2</v>
       </c>
       <c r="P4" s="57">
         <f>SUM($O$4:O4)</f>
-        <v>62.900000000000006</v>
+        <v>45.2</v>
       </c>
       <c r="Q4" s="58">
         <f ca="1">IF(M4=0,IF(P4=0,0,"期限切れ"),P4/M4)</f>
-        <v>3.4944444444444449</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="18" customHeight="1">
@@ -5460,7 +5589,7 @@
       </c>
       <c r="M5" s="56">
         <f ca="1">MAX(0,L5-TODAY()+1)</f>
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="N5" s="57">
         <f>SUMIF(タスク[バージョン],J5,タスク[作業工数])</f>
@@ -5472,11 +5601,11 @@
       </c>
       <c r="P5" s="57">
         <f>SUM($O$4:O5)</f>
-        <v>109.9</v>
+        <v>92.2</v>
       </c>
       <c r="Q5" s="58">
         <f ca="1">IF(M5=0,IF(P5=0,0,"期限切れ"),P5/M5)</f>
-        <v>2.2895833333333333</v>
+        <v>2.7117647058823531</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="18" customHeight="1">
@@ -5519,7 +5648,7 @@
       </c>
       <c r="M6" s="56">
         <f ca="1">MAX(0,L6-TODAY()+1)</f>
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="N6" s="57">
         <f>SUMIF(タスク[バージョン],J6,タスク[作業工数])</f>
@@ -5531,11 +5660,11 @@
       </c>
       <c r="P6" s="57">
         <f>SUM($O$4:O6)</f>
-        <v>124.4</v>
+        <v>106.7</v>
       </c>
       <c r="Q6" s="58">
         <f ca="1">IF(M6=0,IF(P6=0,0,"期限切れ"),P6/M6)</f>
-        <v>1.9746031746031747</v>
+        <v>2.1775510204081634</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="18" customHeight="1">
@@ -5578,7 +5707,7 @@
       </c>
       <c r="M7" s="56">
         <f ca="1">MAX(0,L7-TODAY()+1)</f>
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="N7" s="57">
         <f>SUMIF(タスク[バージョン],J7,タスク[作業工数])</f>
@@ -5590,11 +5719,11 @@
       </c>
       <c r="P7" s="57">
         <f>SUM($O$4:O7)</f>
-        <v>133.4</v>
+        <v>115.7</v>
       </c>
       <c r="Q7" s="58">
         <f ca="1">IF(M7=0,IF(P7=0,0,"期限切れ"),P7/M7)</f>
-        <v>1.7102564102564104</v>
+        <v>1.8078125</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="18" customHeight="1">
@@ -5637,7 +5766,7 @@
       </c>
       <c r="M8" s="56">
         <f ca="1">MAX(0,L8-TODAY()+1)</f>
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="N8" s="57">
         <f>SUMIF(タスク[バージョン],J8,タスク[作業工数])</f>
@@ -5649,11 +5778,11 @@
       </c>
       <c r="P8" s="57">
         <f>SUM($O$4:O8)</f>
-        <v>133.4</v>
+        <v>115.7</v>
       </c>
       <c r="Q8" s="58">
         <f ca="1">IF(M8=0,IF(P8=0,0,"期限切れ"),P8/M8)</f>
-        <v>1.688607594936709</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="18" customHeight="1">
@@ -5766,7 +5895,7 @@
       </c>
       <c r="K13" s="64">
         <f ca="1">TODAY()</f>
-        <v>46309</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="14" spans="2:17" ht="18" customHeight="1">
@@ -5803,7 +5932,7 @@
       </c>
       <c r="K14" s="65">
         <f ca="1">MAX(0,TODAY()-K12)</f>
-        <v>20</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="2:17" ht="18" customHeight="1">
@@ -5840,7 +5969,7 @@
       </c>
       <c r="K15" s="65">
         <f ca="1">M8</f>
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="2:17" ht="18" customHeight="1">
@@ -5877,7 +6006,7 @@
       </c>
       <c r="K16" s="66">
         <f>コスト表!M6</f>
-        <v>152.9</v>
+        <v>153.9</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18" customHeight="1">
@@ -5914,7 +6043,7 @@
       </c>
       <c r="K17" s="66">
         <f>コスト表!N6</f>
-        <v>19.5</v>
+        <v>38.200000000000003</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="18" customHeight="1">
@@ -5951,7 +6080,7 @@
       </c>
       <c r="K18" s="66">
         <f>K16-K17</f>
-        <v>133.4</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18" customHeight="1">
@@ -5960,7 +6089,7 @@
       </c>
       <c r="K19" s="67">
         <f>IF(K16=0,0,K17/K16)</f>
-        <v>0.12753433616742968</v>
+        <v>0.24821312540610788</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18" customHeight="1">
@@ -5979,7 +6108,7 @@
       </c>
       <c r="K20" s="68">
         <f ca="1">IF(K14=0,0,K17/K14)</f>
-        <v>0.97499999999999998</v>
+        <v>1.1235294117647059</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="18" customHeight="1">
@@ -6009,7 +6138,7 @@
       </c>
       <c r="K21" s="68">
         <f ca="1">IF(K15=0,"-",K18/K15)</f>
-        <v>1.688607594936709</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="18" customHeight="1">

--- a/winterGame2026/冬制作_2026コスト表.xlsx
+++ b/winterGame2026/冬制作_2026コスト表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kawanamihakuto\Desktop\GitHub\2026_winter\winterGame2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E87DF5C-047F-4016-9C73-8797A35D616E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F636D223-D35C-48D6-A0F5-7B3DB4783337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11295" xr2:uid="{FBF17539-65CE-42B3-B6F8-B994C8DD201F}"/>
+    <workbookView xWindow="5130" yWindow="3180" windowWidth="21600" windowHeight="11295" xr2:uid="{FBF17539-65CE-42B3-B6F8-B994C8DD201F}"/>
   </bookViews>
   <sheets>
     <sheet name="コスト表" sheetId="1" r:id="rId1"/>
@@ -1057,7 +1057,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1298,23 +1298,14 @@
     <xf numFmtId="0" fontId="5" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="55" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2187,15 +2178,15 @@
       </c>
       <c r="N6" s="45">
         <f>SUMIF(タスク[ステータス],"完了",タスク[作業工数])</f>
-        <v>38.200000000000003</v>
+        <v>42.2</v>
       </c>
       <c r="O6" s="45">
         <f>M6-N6</f>
-        <v>115.7</v>
+        <v>111.7</v>
       </c>
       <c r="P6" s="47">
         <f>IF(M6=0,0,N6/M6)</f>
-        <v>0.24821312540610788</v>
+        <v>0.27420402858999349</v>
       </c>
     </row>
     <row r="7" spans="2:16">
@@ -2233,15 +2224,15 @@
       </c>
       <c r="N7" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[バージョン],L7,タスク[ステータス],"完了")</f>
-        <v>38.200000000000003</v>
+        <v>42.2</v>
       </c>
       <c r="O7" s="45">
         <f>M7-N7</f>
-        <v>45.2</v>
+        <v>41.2</v>
       </c>
       <c r="P7" s="47">
         <f>IF(M7=0,0,N7/M7)</f>
-        <v>0.45803357314148679</v>
+        <v>0.50599520383693042</v>
       </c>
     </row>
     <row r="8" spans="2:16">
@@ -2536,15 +2527,15 @@
       </c>
       <c r="N14" s="45">
         <f>SUMIFS(タスク[作業工数],タスク[概要],L14,タスク[ステータス],"完了")</f>
-        <v>5.5</v>
+        <v>9.5</v>
       </c>
       <c r="O14" s="45">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P14" s="47">
         <f t="shared" si="1"/>
-        <v>0.40740740740740738</v>
+        <v>0.70370370370370372</v>
       </c>
     </row>
     <row r="15" spans="2:16">
@@ -2568,7 +2559,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="J15" t="s">
         <v>27</v>
@@ -2614,7 +2605,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J16" t="s">
         <v>27</v>
@@ -2706,7 +2697,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
         <v>39</v>
@@ -3239,11 +3230,11 @@
       </c>
       <c r="M30" s="25">
         <f>COUNTIF(タスク[ステータス],L30)</f>
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N30" s="45">
         <f>SUMIF(タスク[ステータス],L30,タスク[作業工数])</f>
-        <v>106.2</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="31" spans="2:16">
@@ -3315,11 +3306,11 @@
       </c>
       <c r="M32" s="25">
         <f>COUNTIF(タスク[ステータス],L32)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N32" s="45">
         <f>SUMIF(タスク[ステータス],L32,タスク[作業工数])</f>
-        <v>38.200000000000003</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="33" spans="2:14">
@@ -4111,29 +4102,29 @@
       </c>
     </row>
     <row r="61" spans="2:10">
-      <c r="B61" s="82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="85" t="s">
+      <c r="B61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="D61" s="83" t="s">
+      <c r="D61" t="s">
         <v>216</v>
       </c>
-      <c r="E61" s="83" t="s">
+      <c r="E61" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="83" t="s">
+      <c r="F61" t="s">
         <v>13</v>
       </c>
-      <c r="G61" s="84">
+      <c r="G61" s="3">
         <v>1</v>
       </c>
-      <c r="H61" s="84"/>
-      <c r="I61" s="83" t="s">
+      <c r="H61" s="3"/>
+      <c r="I61" t="s">
         <v>34</v>
       </c>
-      <c r="J61" s="83" t="s">
+      <c r="J61" t="s">
         <v>217</v>
       </c>
     </row>
@@ -5429,16 +5420,16 @@
   <sheetData>
     <row r="1" spans="2:17" ht="18" customHeight="1"/>
     <row r="2" spans="2:17" ht="18" customHeight="1">
-      <c r="B2" s="80">
+      <c r="B2" s="81">
         <f>DATE(2026,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
       <c r="J2" s="52" t="s">
         <v>164</v>
       </c>
@@ -5538,15 +5529,15 @@
       </c>
       <c r="O4" s="57">
         <f>N4-SUMIFS(タスク[作業工数],タスク[バージョン],J4,タスク[ステータス],"完了")</f>
-        <v>45.2</v>
+        <v>41.2</v>
       </c>
       <c r="P4" s="57">
         <f>SUM($O$4:O4)</f>
-        <v>45.2</v>
+        <v>41.2</v>
       </c>
       <c r="Q4" s="58">
         <f ca="1">IF(M4=0,IF(P4=0,0,"期限切れ"),P4/M4)</f>
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="18" customHeight="1">
@@ -5601,11 +5592,11 @@
       </c>
       <c r="P5" s="57">
         <f>SUM($O$4:O5)</f>
-        <v>92.2</v>
+        <v>88.2</v>
       </c>
       <c r="Q5" s="58">
         <f ca="1">IF(M5=0,IF(P5=0,0,"期限切れ"),P5/M5)</f>
-        <v>2.7117647058823531</v>
+        <v>2.5941176470588236</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="18" customHeight="1">
@@ -5660,11 +5651,11 @@
       </c>
       <c r="P6" s="57">
         <f>SUM($O$4:O6)</f>
-        <v>106.7</v>
+        <v>102.7</v>
       </c>
       <c r="Q6" s="58">
         <f ca="1">IF(M6=0,IF(P6=0,0,"期限切れ"),P6/M6)</f>
-        <v>2.1775510204081634</v>
+        <v>2.0959183673469388</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="18" customHeight="1">
@@ -5719,11 +5710,11 @@
       </c>
       <c r="P7" s="57">
         <f>SUM($O$4:O7)</f>
-        <v>115.7</v>
+        <v>111.7</v>
       </c>
       <c r="Q7" s="58">
         <f ca="1">IF(M7=0,IF(P7=0,0,"期限切れ"),P7/M7)</f>
-        <v>1.8078125</v>
+        <v>1.7453125</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="18" customHeight="1">
@@ -5778,11 +5769,11 @@
       </c>
       <c r="P8" s="57">
         <f>SUM($O$4:O8)</f>
-        <v>115.7</v>
+        <v>111.7</v>
       </c>
       <c r="Q8" s="58">
         <f ca="1">IF(M8=0,IF(P8=0,0,"期限切れ"),P8/M8)</f>
-        <v>1.78</v>
+        <v>1.7184615384615385</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="18" customHeight="1">
@@ -5817,16 +5808,16 @@
     </row>
     <row r="10" spans="2:17" ht="18" customHeight="1"/>
     <row r="11" spans="2:17" ht="18" customHeight="1">
-      <c r="B11" s="80">
+      <c r="B11" s="81">
         <f>DATE(2026,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="81"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="82"/>
+      <c r="E11" s="82"/>
+      <c r="F11" s="82"/>
+      <c r="G11" s="82"/>
+      <c r="H11" s="82"/>
       <c r="J11" s="52" t="s">
         <v>171</v>
       </c>
@@ -6043,7 +6034,7 @@
       </c>
       <c r="K17" s="66">
         <f>コスト表!N6</f>
-        <v>38.200000000000003</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="18" customHeight="1">
@@ -6080,7 +6071,7 @@
       </c>
       <c r="K18" s="66">
         <f>K16-K17</f>
-        <v>115.7</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18" customHeight="1">
@@ -6089,26 +6080,26 @@
       </c>
       <c r="K19" s="67">
         <f>IF(K16=0,0,K17/K16)</f>
-        <v>0.24821312540610788</v>
+        <v>0.27420402858999349</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18" customHeight="1">
-      <c r="B20" s="80">
+      <c r="B20" s="81">
         <f>DATE(2026,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
+      <c r="C20" s="82"/>
+      <c r="D20" s="82"/>
+      <c r="E20" s="82"/>
+      <c r="F20" s="82"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="82"/>
       <c r="J20" s="63" t="s">
         <v>176</v>
       </c>
       <c r="K20" s="68">
         <f ca="1">IF(K14=0,0,K17/K14)</f>
-        <v>1.1235294117647059</v>
+        <v>1.2411764705882353</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="18" customHeight="1">
@@ -6138,7 +6129,7 @@
       </c>
       <c r="K21" s="68">
         <f ca="1">IF(K15=0,"-",K18/K15)</f>
-        <v>1.78</v>
+        <v>1.7184615384615385</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="18" customHeight="1">
@@ -6353,16 +6344,16 @@
       </c>
     </row>
     <row r="29" spans="2:11" ht="18" customHeight="1">
-      <c r="B29" s="80">
+      <c r="B29" s="81">
         <f>DATE(2026,12,1)</f>
         <v>46357</v>
       </c>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
+      <c r="C29" s="82"/>
+      <c r="D29" s="82"/>
+      <c r="E29" s="82"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="82"/>
+      <c r="H29" s="82"/>
       <c r="J29" s="71" t="s">
         <v>182</v>
       </c>
